--- a/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0002T0006Z000C1N3_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T0374L_W0041F0002T0006Z000C1N3_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>38.23939031693235</v>
+        <v>6.213900926501507</v>
       </c>
       <c r="D2" t="n">
-        <v>38.53908169418627</v>
+        <v>6.26260077530527</v>
       </c>
       <c r="E2" t="n">
-        <v>4.543072649254766</v>
+        <v>0.7382493055038997</v>
       </c>
       <c r="F2" t="n">
-        <v>4.521606048799748</v>
+        <v>0.7347609829299588</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>41.46753749394443</v>
+        <v>6.73847484276597</v>
       </c>
       <c r="D3" t="n">
-        <v>41.32103082889201</v>
+        <v>6.714667509694952</v>
       </c>
       <c r="E3" t="n">
-        <v>4.543072649254766</v>
+        <v>0.7382493055038997</v>
       </c>
       <c r="F3" t="n">
-        <v>4.521606048799748</v>
+        <v>0.7347609829299588</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>35.61533260690913</v>
+        <v>5.787491548622735</v>
       </c>
       <c r="D4" t="n">
-        <v>35.27012330186816</v>
+        <v>5.731395036553576</v>
       </c>
       <c r="E4" t="n">
-        <v>4.543072649254766</v>
+        <v>0.7382493055038997</v>
       </c>
       <c r="F4" t="n">
-        <v>4.521606048799748</v>
+        <v>0.7347609829299588</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>29.10458261690226</v>
+        <v>4.729494675246617</v>
       </c>
       <c r="D5" t="n">
-        <v>29.18012166104115</v>
+        <v>4.741769769919188</v>
       </c>
       <c r="E5" t="n">
-        <v>4.543072649254766</v>
+        <v>0.7382493055038997</v>
       </c>
       <c r="F5" t="n">
-        <v>4.521606048799748</v>
+        <v>0.7347609829299588</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
